--- a/CDF_Batt_Cost/SplineCDF_Fall2025_Batt Cost.xlsx
+++ b/CDF_Batt_Cost/SplineCDF_Fall2025_Batt Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Batt_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB51798-596E-4A24-B394-385E9E5C80DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{3FB51798-596E-4A24-B394-385E9E5C80DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A120F285-80F9-496F-A0E8-C9E68657C367}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6583,127 +6583,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>1</v>
+        <v>0.11932921058941499</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.33749999999999997</v>
+        <v>0.10841535387238249</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.35</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>0</v>
+        <v>1.6666666666666677E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-5.5511151231257827E-17</v>
+        <v>-1.6666666666666691E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-0.19999999999999996</v>
+        <v>-1.9329210589414988E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.99999999999999978</v>
+        <v>0.38658421178829977</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.75</v>
+        <v>0.45585088965459519</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.75</v>
-      </c>
-      <c r="M2" t="e">
+        <v>0.45585088965459519</v>
+      </c>
+      <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N2" t="e">
+        <v>2.6666666666666643</v>
+      </c>
+      <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O2" t="e">
+        <v>-0.23382670943897263</v>
+      </c>
+      <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>#DIV/0!</v>
+        <v>0.7160006941029835</v>
       </c>
       <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="Q2" t="e">
         <f ca="1">P2^(1/3)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="R2" t="e">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="S2" t="e">
         <f ca="1">-Q2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="T2" t="e">
         <f ca="1">COS(R2/3)</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="U2" t="e">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>#DIV/0!</v>
+        <v>0.33333333333333365</v>
       </c>
       <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="X2" t="e">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>#DIV/0!</v>
+        <v>#NUM!</v>
       </c>
       <c r="Y2" t="e">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z2">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>0.96308159691661788</v>
+      </c>
+      <c r="AA2">
         <f ca="1">Z2^(1/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2" t="e">
+        <v>0.98753924002946858</v>
+      </c>
+      <c r="AB2">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2" t="e">
+        <v>-0.72925488747764533</v>
+      </c>
+      <c r="AC2">
         <f ca="1">AB2^(1/3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2" t="e">
+        <v>-0.90010487974367814</v>
+      </c>
+      <c r="AD2">
         <f ca="1">AA2+AC2+V2</f>
-        <v>#DIV/0!</v>
+        <v>0.42076769361912408</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.75</v>
+        <v>0.42076769361912408</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36537,15 +36537,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36683,6 +36674,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36690,14 +36690,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CEDDE7-0E5B-49B8-A433-7DC008954906}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C145F7C7-0795-444C-A713-E3D3E73240A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36715,6 +36707,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CEDDE7-0E5B-49B8-A433-7DC008954906}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7D35D2-9058-48D0-B447-5DB03C60D6A8}">
   <ds:schemaRefs>

--- a/CDF_Batt_Cost/SplineCDF_Fall2025_Batt Cost.xlsx
+++ b/CDF_Batt_Cost/SplineCDF_Fall2025_Batt Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Batt_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{3FB51798-596E-4A24-B394-385E9E5C80DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A120F285-80F9-496F-A0E8-C9E68657C367}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{3FB51798-596E-4A24-B394-385E9E5C80DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FF50F34-4C1C-455D-B3B5-F64432E99AD3}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4825,6 +4825,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6583,127 +6587,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.11932921058941499</v>
+        <v>0.161906120264249</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.10841535387238249</v>
+        <v>0.12297417796050657</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.1</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.12000000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>1.6666666666666677E-2</v>
+        <v>-6.666666666666668E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>-1.6666666666666691E-2</v>
+        <v>0.10000000000000003</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>0.05</v>
+        <v>6.6666666666666652E-2</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-1.9329210589414988E-2</v>
+        <v>-1.1906120264249004E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.38658421178829977</v>
+        <v>0.17859180396373509</v>
       </c>
       <c r="K2">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.45585088965459519</v>
+        <v>0.14642943486945373</v>
       </c>
       <c r="L2">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.45585088965459519</v>
+        <v>0.14642943486945373</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>2.6666666666666643</v>
+        <v>-1.75</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-0.23382670943897263</v>
+        <v>-0.57140819603626491</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>0.7160006941029835</v>
-      </c>
-      <c r="P2" t="e">
+        <v>-0.11686853874601574</v>
+      </c>
+      <c r="P2">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="Q2" t="e">
+        <v>0.44552819256515114</v>
+      </c>
+      <c r="Q2">
         <f ca="1">P2^(1/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="R2" t="e">
+        <v>0.76376261582597338</v>
+      </c>
+      <c r="R2">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="S2" t="e">
+        <v>0.87464339773044086</v>
+      </c>
+      <c r="S2">
         <f ca="1">-Q2</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="T2" t="e">
+        <v>-0.76376261582597338</v>
+      </c>
+      <c r="T2">
         <f ca="1">COS(R2/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="U2" t="e">
+        <v>0.95780013122791696</v>
+      </c>
+      <c r="U2">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>#NUM!</v>
+        <v>0.49785211243837779</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0.33333333333333365</v>
-      </c>
-      <c r="W2" t="e">
+        <v>0.50000000000000011</v>
+      </c>
+      <c r="W2">
         <f ca="1">2*Q2*T2+V2</f>
+        <v>1.963063867330189</v>
+      </c>
+      <c r="X2">
+        <f ca="1">S2*(T2+U2)+V2</f>
+        <v>-0.61177276535551639</v>
+      </c>
+      <c r="Y2">
+        <f ca="1">S2*(T2-U2)+V2</f>
+        <v>0.14870889802532772</v>
+      </c>
+      <c r="Z2" t="e">
+        <f ca="1">-N2/2+SQRT(O2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="X2" t="e">
-        <f ca="1">S2*(T2+U2)+V2</f>
+      <c r="AA2" t="e">
+        <f ca="1">Z2^(1/3)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Y2" t="e">
-        <f ca="1">S2*(T2-U2)+V2</f>
+      <c r="AB2" t="e">
+        <f ca="1">-N2/2-SQRT(O2)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z2">
-        <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>0.96308159691661788</v>
-      </c>
-      <c r="AA2">
-        <f ca="1">Z2^(1/3)</f>
-        <v>0.98753924002946858</v>
-      </c>
-      <c r="AB2">
-        <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>-0.72925488747764533</v>
-      </c>
-      <c r="AC2">
+      <c r="AC2" t="e">
         <f ca="1">AB2^(1/3)</f>
-        <v>-0.90010487974367814</v>
-      </c>
-      <c r="AD2">
+        <v>#NUM!</v>
+      </c>
+      <c r="AD2" t="e">
         <f ca="1">AA2+AC2+V2</f>
-        <v>0.42076769361912408</v>
+        <v>#NUM!</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.42076769361912408</v>
+        <v>0.14870889802532772</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36537,6 +36541,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010000B92449D07C8D4B9A11B36D3DD1493B" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="12876fd8bd5d90ce750491db8e9e67c2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18b8549e-3e0d-4ec5-af2b-e3bc54260487" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45151d2993f903c2059e1e395416a0b1" ns2:_="">
     <xsd:import namespace="18b8549e-3e0d-4ec5-af2b-e3bc54260487"/>
@@ -36674,15 +36687,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -36690,6 +36694,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CEDDE7-0E5B-49B8-A433-7DC008954906}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C145F7C7-0795-444C-A713-E3D3E73240A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36707,14 +36719,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CEDDE7-0E5B-49B8-A433-7DC008954906}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7D35D2-9058-48D0-B447-5DB03C60D6A8}">
   <ds:schemaRefs>

--- a/CDF_Batt_Cost/SplineCDF_Fall2025_Batt Cost.xlsx
+++ b/CDF_Batt_Cost/SplineCDF_Fall2025_Batt Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/CDF_Batt_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="13_ncr:1_{3FB51798-596E-4A24-B394-385E9E5C80DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FF50F34-4C1C-455D-B3B5-F64432E99AD3}"/>
+  <xr:revisionPtr revIDLastSave="1354" documentId="13_ncr:1_{3FB51798-596E-4A24-B394-385E9E5C80DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C019CA72-11F6-448C-A368-8D70904E2718}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6587,127 +6587,127 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
-        <v>0.161906120264249</v>
+        <v>0.144081122243334</v>
       </c>
       <c r="B2" s="7">
         <f ca="1">IF(AND(A2&gt;=0,A2&lt;=1),D2+AE2*(E2-D2),"")</f>
-        <v>0.12297417796050657</v>
+        <v>0.11814204531483499</v>
       </c>
       <c r="C2">
         <f ca="1">IF(A2&lt;1,LOOKUP(A2,Computations!$C$2:$C$100,Computations!$A$2:$A$100),n)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <f ca="1">INDIRECT("Computations!B"&amp;C2)</f>
-        <v>0.12000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
         <f ca="1">INDIRECT("Computations!B"&amp;(C2+1))</f>
-        <v>0.14000000000000001</v>
+        <v>0.12000000000000001</v>
       </c>
       <c r="F2">
         <f ca="1">INDIRECT("Computations!S"&amp;C2)</f>
-        <v>-6.666666666666668E-2</v>
+        <v>1.6666666666666677E-2</v>
       </c>
       <c r="G2">
         <f ca="1">INDIRECT("Computations!R"&amp;C2)</f>
-        <v>0.10000000000000003</v>
+        <v>-1.6666666666666691E-2</v>
       </c>
       <c r="H2">
         <f ca="1">INDIRECT("Computations!Q"&amp;C2)</f>
-        <v>6.6666666666666652E-2</v>
+        <v>0.05</v>
       </c>
       <c r="I2">
         <f ca="1">INDIRECT("Computations!C"&amp;C2)-A2</f>
-        <v>-1.1906120264249004E-2</v>
+        <v>-4.4081122243333992E-2</v>
       </c>
       <c r="J2">
         <f ca="1">-I2/H2</f>
-        <v>0.17859180396373509</v>
-      </c>
-      <c r="K2">
+        <v>0.88162244486667984</v>
+      </c>
+      <c r="K2" t="e">
         <f ca="1">(-H2+SQRT(H2*H2-4*G2*I2))/(2*G2)</f>
-        <v>0.14642943486945373</v>
-      </c>
-      <c r="L2">
+        <v>#NUM!</v>
+      </c>
+      <c r="L2" t="e">
         <f ca="1">IF(AND(K2&gt;=0,K2&lt;=1),K2,(-H2-SQRT(H2*H2-4*G2*I2))/(2*G2))</f>
-        <v>0.14642943486945373</v>
+        <v>#NUM!</v>
       </c>
       <c r="M2">
         <f ca="1">H2/F2-G2^2/F2^2/3</f>
-        <v>-1.75</v>
+        <v>2.6666666666666643</v>
       </c>
       <c r="N2">
         <f ca="1">(2*G2^3/F2^3-9*G2*H2/F2^2+27*I2/F2)/27</f>
-        <v>-0.57140819603626491</v>
+        <v>-1.7189414086741119</v>
       </c>
       <c r="O2">
         <f ca="1">N2^2/4+M2^3/27</f>
-        <v>-0.11686853874601574</v>
-      </c>
-      <c r="P2">
+        <v>1.441021853204854</v>
+      </c>
+      <c r="P2" t="e">
         <f ca="1">SQRT(N2^2/4-O2)</f>
-        <v>0.44552819256515114</v>
-      </c>
-      <c r="Q2">
+        <v>#NUM!</v>
+      </c>
+      <c r="Q2" t="e">
         <f ca="1">P2^(1/3)</f>
-        <v>0.76376261582597338</v>
-      </c>
-      <c r="R2">
+        <v>#NUM!</v>
+      </c>
+      <c r="R2" t="e">
         <f ca="1">ACOS(-N2/2/P2)</f>
-        <v>0.87464339773044086</v>
-      </c>
-      <c r="S2">
+        <v>#NUM!</v>
+      </c>
+      <c r="S2" t="e">
         <f ca="1">-Q2</f>
-        <v>-0.76376261582597338</v>
-      </c>
-      <c r="T2">
+        <v>#NUM!</v>
+      </c>
+      <c r="T2" t="e">
         <f ca="1">COS(R2/3)</f>
-        <v>0.95780013122791696</v>
-      </c>
-      <c r="U2">
+        <v>#NUM!</v>
+      </c>
+      <c r="U2" t="e">
         <f ca="1">SQRT(3)*SIN(R2/3)</f>
-        <v>0.49785211243837779</v>
+        <v>#NUM!</v>
       </c>
       <c r="V2">
         <f ca="1">-G2/F2/3</f>
-        <v>0.50000000000000011</v>
-      </c>
-      <c r="W2">
+        <v>0.33333333333333365</v>
+      </c>
+      <c r="W2" t="e">
         <f ca="1">2*Q2*T2+V2</f>
-        <v>1.963063867330189</v>
-      </c>
-      <c r="X2">
+        <v>#NUM!</v>
+      </c>
+      <c r="X2" t="e">
         <f ca="1">S2*(T2+U2)+V2</f>
-        <v>-0.61177276535551639</v>
-      </c>
-      <c r="Y2">
+        <v>#NUM!</v>
+      </c>
+      <c r="Y2" t="e">
         <f ca="1">S2*(T2-U2)+V2</f>
-        <v>0.14870889802532772</v>
-      </c>
-      <c r="Z2" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="Z2">
         <f ca="1">-N2/2+SQRT(O2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AA2" t="e">
+        <v>2.059896400998392</v>
+      </c>
+      <c r="AA2">
         <f ca="1">Z2^(1/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB2" t="e">
+        <v>1.2723749967716818</v>
+      </c>
+      <c r="AB2">
         <f ca="1">-N2/2-SQRT(O2)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC2" t="e">
+        <v>-0.34095499232428006</v>
+      </c>
+      <c r="AC2">
         <f ca="1">AB2^(1/3)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AD2" t="e">
+        <v>-0.69860606436326611</v>
+      </c>
+      <c r="AD2">
         <f ca="1">AA2+AC2+V2</f>
-        <v>#NUM!</v>
+        <v>0.90710226574174935</v>
       </c>
       <c r="AE2">
         <f ca="1">IF(F2=0,IF(G2=0,J2,L2),IF(O2&gt;0,AD2,IF(AND(W2&gt;=0,W2&lt;=1),W2,IF(AND(X2&gt;=0,X2&lt;=1),X2,Y2))))</f>
-        <v>0.14870889802532772</v>
+        <v>0.90710226574174935</v>
       </c>
       <c r="AG2" t="s">
         <v>58</v>
@@ -36541,12 +36541,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36688,15 +36685,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CEDDE7-0E5B-49B8-A433-7DC008954906}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7D35D2-9058-48D0-B447-5DB03C60D6A8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36720,10 +36721,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D7D35D2-9058-48D0-B447-5DB03C60D6A8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7CEDDE7-0E5B-49B8-A433-7DC008954906}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>